--- a/Extended Data Fig. 18 Estimated NH4+ production profile. Comparation between the approximate calculation and direct calculation.xlsx
+++ b/Extended Data Fig. 18 Estimated NH4+ production profile. Comparation between the approximate calculation and direct calculation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\金星NC修改\数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\二审意见\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749E0038-98C8-4DD7-8EC8-F05706270B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C92A70-782F-4686-A5ED-341AA67F8C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Approximate calculation" sheetId="1" r:id="rId1"/>
@@ -28,10 +28,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
   <si>
-    <t>高度/km</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>S8/(mol/km)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -43,12 +39,16 @@
     <t>S7/(mol/km)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Altitude/km</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,10 +67,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -93,9 +97,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -379,552 +384,554 @@
   <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="4" width="12.4140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>48</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>8134706893517.832</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>665793055586.11926</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>686506058450.13403</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>49</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>6601125096189.4951</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>474005870855.07501</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>492322765126.9649</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>50</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>5230453525174.5498</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>348137591724.60162</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>334689224170.53528</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>51</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>3932357914231.3779</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>227548227032.30469</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>219758959834.08661</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>52</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>2948696642745.6582</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>138608978774.24039</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>121672635380.73869</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>53</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>1812503035006.5569</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>78494065731.490646</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>59570784877.716133</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>54</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>1054660467709.79</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>31818416435.446018</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>21488808027.29958</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>55</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>569817829133.5564</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>12460970950.567671</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>8110376743.3776808</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>56</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>246155719360.96939</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>4169899753.655962</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>3241193974.2820468</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>57</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>113355487658.6185</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>1439336574.8725221</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>1319630745.5269589</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="A12" s="2">
         <v>58</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>71228702095.816833</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>645946289.5403229</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>628995545.41733754</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="A13" s="2">
         <v>59</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>47192787576.828087</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>441940987.02256989</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>351112915.6564737</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="A14" s="2">
         <v>60</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>31459975630.301289</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>264362324.76655191</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>186557266.1527012</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="A15" s="2">
         <v>61</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>33921476637.740742</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>221606291.84123129</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>176200112.56787211</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="A16" s="2">
         <v>62</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>21461386642.135891</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>123297204.5515537</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>100001639.08748829</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="A17" s="2">
         <v>63</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="2">
         <v>14781721202.069901</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>61797202.65538162</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>49016862.087646157</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="A18" s="2">
         <v>64</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <v>8256100633.7362099</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2">
         <v>27097951.742613081</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>19215906.409000989</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="A19" s="2">
         <v>65</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
         <v>4599341436.7469893</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2">
         <v>13625857.3313445</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>8838013.7408727501</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="2">
         <v>66</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <v>2517074217.0316229</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2">
         <v>7574825.8761892784</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>5470629.0669677462</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="2">
         <v>67</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <v>1363309699.0774159</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>4192578.509011941</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>3069985.8747305861</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="A22" s="2">
         <v>68</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
         <v>783674742.10426044</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <v>2662588.3937016302</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>1653095.9765613461</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="A23" s="2">
         <v>69</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
         <v>609907128.53539944</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2">
         <v>2099538.884618971</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>1305503.3975388231</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="A24" s="2">
         <v>70</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="2">
         <v>350728242.856309</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2">
         <v>1225679.7446664399</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>693617.65596903907</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="A25" s="2">
         <v>71</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="2">
         <v>270295429.49089462</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2">
         <v>920620.21333052113</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>462473.70529520517</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26">
+      <c r="A26" s="2">
         <v>72</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
         <v>235368949.09142649</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2">
         <v>753145.79154929519</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>383568.43219295028</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27">
+      <c r="A27" s="2">
         <v>73</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
         <v>274170798.30076569</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2">
         <v>892485.51319612376</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>429759.33921611792</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28">
+      <c r="A28" s="2">
         <v>74</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
         <v>386917835.80562139</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2">
         <v>1229205.812000986</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>632735.98287300591</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29">
+      <c r="A29" s="2">
         <v>75</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
         <v>269398755.38981003</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2">
         <v>873959.05544793757</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>432846.04520096892</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30">
+      <c r="A30" s="2">
         <v>76</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="2">
         <v>89899898.541138798</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="2">
         <v>250296.02024043791</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="2">
         <v>131950.2265030428</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31">
+      <c r="A31" s="2">
         <v>77</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="2">
         <v>21583454.20814475</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="2">
         <v>43501.185760742723</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="2">
         <v>25859.101715607441</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="A32" s="2">
         <v>78</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="2">
         <v>2087921.58769543</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="2">
         <v>3505.2338693699958</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="2">
         <v>1317.497301416953</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="A33" s="2">
         <v>79</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="2">
         <v>305280.72229029849</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="2">
         <v>408.9407287514652</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="2">
         <v>123.6865401384282</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="A34" s="2">
         <v>80</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="2">
         <v>62022.382462479582</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="2">
         <v>69.262168233641418</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="2">
         <v>23.25745879707107</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="A35" s="2">
         <v>81</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="2">
         <v>17668.431607259459</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="2">
         <v>19.46482479223581</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="2">
         <v>5.5130513336680522</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="A36" s="2">
         <v>82</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="2">
         <v>7261.0382419130183</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="2">
         <v>7.5538743590922781</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="2">
         <v>1.8829641920051901</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37">
+      <c r="A37" s="2">
         <v>83</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="2">
         <v>2478.636986661023</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="2">
         <v>2.2643735097006008</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="2">
         <v>0.55266404345867315</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="A38" s="2">
         <v>84</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="2">
         <v>682.14171814329757</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="2">
         <v>0.56651758745039171</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="2">
         <v>0.14021568425776121</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="A39" s="2">
         <v>85</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="2">
         <v>188.83709850276301</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="2">
         <v>0.1430135868051336</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="2">
         <v>3.4357611986496867E-2</v>
       </c>
     </row>
@@ -939,553 +946,554 @@
   <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.4140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>48</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>3382186750268.959</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>639850836486.53113</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>646516138611.73779</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>49</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>3813965830917.6611</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>464557560752.31958</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>477838383981.03418</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>50</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>3841233656311.0439</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>344612724142.69531</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>330267186923.67877</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>51</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>3362825956462.377</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>226492059689.0986</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>218477807277.68799</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>52</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>2732016344435.9302</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>138334636767.78021</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>121405760383.8772</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>53</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>1759050108271.5439</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>78427279974.708572</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>59521296092.746429</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>54</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>1043644781951.566</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>31807017609.407982</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>21481841162.686859</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>55</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>567736739544.98706</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>12458168876.798969</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>8108655226.2809486</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>56</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>245893357715.81439</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>4169109504.517066</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>3240585722.0885882</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>57</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>113310949302.9884</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>1439074658.104645</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>1319390804.833329</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="A12" s="2">
         <v>58</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>71211320983.696487</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>645829666.85096562</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>628881982.82562637</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="A13" s="2">
         <v>59</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>47183224827.300728</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>441861304.3339594</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>351049619.60283571</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="A14" s="2">
         <v>60</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>31454055616.96106</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>264314685.27578959</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>186523650.11902711</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="A15" s="2">
         <v>61</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>33915256084.25967</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>221566364.23846799</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>176168366.47286329</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="A16" s="2">
         <v>62</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>21457488898.353649</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>123274990.7232818</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>99983622.398016959</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="A17" s="2">
         <v>63</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="2">
         <v>14779045964.63089</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>61786069.16784288</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>49008031.148181424</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="A18" s="2">
         <v>64</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <v>8254609440.1708965</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2">
         <v>27093069.766415481</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>19212444.46941305</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="A19" s="2">
         <v>65</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
         <v>4598511664.7647629</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2">
         <v>13623402.49902674</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>8836421.4871612117</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="2">
         <v>66</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <v>2516620398.2909412</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2">
         <v>7573461.198397452</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>5469643.480869987</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="2">
         <v>67</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <v>1363063986.5088301</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>4191823.176144456</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>3069432.7877005949</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="A22" s="2">
         <v>68</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
         <v>783533523.65348589</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <v>2662108.7032444598</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>1652798.155753887</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="A23" s="2">
         <v>69</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
         <v>609797228.64845347</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2">
         <v>2099160.6328889378</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>1305268.198822808</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="A24" s="2">
         <v>70</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="2">
         <v>350665049.55887568</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2">
         <v>1225458.926938562</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>693492.69423953677</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="A25" s="2">
         <v>71</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="2">
         <v>270246729.60449737</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2">
         <v>920454.35495494097</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>462390.38632138987</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26">
+      <c r="A26" s="2">
         <v>72</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
         <v>235326542.44597659</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2">
         <v>753010.10526755347</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>383499.32874490152</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27">
+      <c r="A27" s="2">
         <v>73</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
         <v>274121400.1760115</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2">
         <v>892324.72355221352</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>429681.91404261498</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28">
+      <c r="A28" s="2">
         <v>74</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
         <v>386848121.6896984</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2">
         <v>1228984.359021723</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>632621.98955045652</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29">
+      <c r="A29" s="2">
         <v>75</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
         <v>269350216.87838578</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2">
         <v>873801.60351763258</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>432768.06392790889</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30">
+      <c r="A30" s="2">
         <v>76</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="2">
         <v>89883701.81529732</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="2">
         <v>250250.9270674994</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="2">
         <v>131926.45443408939</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31">
+      <c r="A31" s="2">
         <v>77</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="2">
         <v>21579565.716495719</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="2">
         <v>43493.348614874318</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="2">
         <v>25854.44295635969</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="A32" s="2">
         <v>78</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="2">
         <v>2087545.428793594</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="2">
         <v>3504.6023686790659</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="2">
         <v>1317.259941946339</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="A33" s="2">
         <v>79</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="2">
         <v>305225.72310565802</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="2">
         <v>408.86705425150939</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="2">
         <v>123.6642568505211</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="A34" s="2">
         <v>80</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="2">
         <v>62011.208549543393</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="2">
         <v>69.249690005744341</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="2">
         <v>23.253268748180592</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="A35" s="2">
         <v>81</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="2">
         <v>17665.248473915071</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="2">
         <v>19.461318021859991</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="2">
         <v>5.51205810586828</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="A36" s="2">
         <v>82</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="2">
         <v>7259.7300979083921</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="2">
         <v>7.5525134579226298</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="2">
         <v>1.8826249583815551</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37">
+      <c r="A37" s="2">
         <v>83</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="2">
         <v>2478.1904370077182</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="2">
         <v>2.2639655616184071</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="2">
         <v>0.55256447585835211</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="A38" s="2">
         <v>84</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="2">
         <v>682.01882392794357</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="2">
         <v>0.56641552400444695</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="2">
         <v>0.1401904230898291</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="A39" s="2">
         <v>85</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="2">
         <v>188.8030777319627</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="2">
         <v>0.14298782156886941</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="2">
         <v>3.4351422141113253E-2</v>
       </c>
     </row>
